--- a/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
+++ b/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1909,7 +1909,6 @@
       <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1942,7 +1941,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1966,7 +1965,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1999,7 +1997,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2023,7 +2021,6 @@
       <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2080,7 +2077,6 @@
       <c r="G5" t="n">
         <v>361</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2137,7 +2133,6 @@
       <c r="G6" t="n">
         <v>310.2</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2194,7 +2189,6 @@
       <c r="G7" t="n">
         <v>447</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2251,7 +2245,6 @@
       <c r="G8" t="n">
         <v>344.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2308,7 +2301,6 @@
       <c r="G9" t="n">
         <v>310.2</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2365,7 +2357,6 @@
       <c r="G10" t="n">
         <v>347.4</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2422,7 +2413,6 @@
       <c r="G11" t="n">
         <v>310.9</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2479,7 +2469,6 @@
       <c r="G12" t="n">
         <v>377.1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2536,7 +2525,6 @@
       <c r="G13" t="n">
         <v>329.2</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2593,7 +2581,6 @@
       <c r="G14" t="n">
         <v>427.2</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2650,7 +2637,6 @@
       <c r="G15" t="n">
         <v>746.2</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2707,7 +2693,6 @@
       <c r="G16" t="n">
         <v>370.8</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2764,7 +2749,6 @@
       <c r="G17" t="n">
         <v>311.7</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2821,7 +2805,6 @@
       <c r="G18" t="n">
         <v>307</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2878,7 +2861,6 @@
       <c r="G19" t="n">
         <v>341.2</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2935,7 +2917,6 @@
       <c r="G20" t="n">
         <v>319.8</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2992,7 +2973,6 @@
       <c r="G21" t="n">
         <v>319.6</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3049,7 +3029,6 @@
       <c r="G22" t="n">
         <v>384.2</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3106,7 +3085,6 @@
       <c r="G23" t="n">
         <v>384.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3163,7 +3141,6 @@
       <c r="G24" t="n">
         <v>384.2</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3220,7 +3197,6 @@
       <c r="G25" t="n">
         <v>384.2</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3277,7 +3253,6 @@
       <c r="G26" t="n">
         <v>337</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3334,7 +3309,6 @@
       <c r="G27" t="n">
         <v>336.6</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3391,7 +3365,6 @@
       <c r="G28" t="n">
         <v>324.2</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3448,7 +3421,6 @@
       <c r="G29" t="n">
         <v>343.5</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3505,7 +3477,6 @@
       <c r="G30" t="n">
         <v>389.3</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3562,7 +3533,6 @@
       <c r="G31" t="n">
         <v>387.8</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3619,7 +3589,6 @@
       <c r="G32" t="n">
         <v>386.9</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3676,7 +3645,6 @@
       <c r="G33" t="n">
         <v>405.1</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3733,7 +3701,6 @@
       <c r="G34" t="n">
         <v>331.4</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3790,7 +3757,6 @@
       <c r="G35" t="n">
         <v>334.7</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3847,7 +3813,6 @@
       <c r="G36" t="n">
         <v>343</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3904,7 +3869,6 @@
       <c r="G37" t="n">
         <v>383.4</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3961,7 +3925,6 @@
       <c r="G38" t="n">
         <v>383.4</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4018,7 +3981,6 @@
       <c r="G39" t="n">
         <v>376.1</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4075,7 +4037,6 @@
       <c r="G40" t="n">
         <v>378.3</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4132,7 +4093,6 @@
       <c r="G41" t="n">
         <v>375</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4189,7 +4149,6 @@
       <c r="G42" t="n">
         <v>376.1</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4246,7 +4205,6 @@
       <c r="G43" t="n">
         <v>456.6</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4303,7 +4261,6 @@
       <c r="G44" t="n">
         <v>293</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4360,7 +4317,6 @@
       <c r="G45" t="n">
         <v>271</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4417,7 +4373,6 @@
       <c r="G46" t="n">
         <v>196</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4474,7 +4429,6 @@
       <c r="G47" t="n">
         <v>193</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4531,7 +4485,6 @@
       <c r="G48" t="n">
         <v>196</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4588,7 +4541,6 @@
       <c r="G49" t="n">
         <v>193</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4645,7 +4597,6 @@
       <c r="G50" t="n">
         <v>283</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4702,7 +4653,6 @@
       <c r="G51" t="n">
         <v>193</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4759,7 +4709,6 @@
       <c r="G52" t="n">
         <v>273</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4816,7 +4765,6 @@
       <c r="G53" t="n">
         <v>411</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4873,7 +4821,6 @@
       <c r="G54" t="n">
         <v>454</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4906,7 +4853,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4930,7 +4877,6 @@
       <c r="G55" t="n">
         <v>120</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4963,7 +4909,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4987,7 +4933,6 @@
       <c r="G56" t="n">
         <v>120</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5020,7 +4965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5044,7 +4989,6 @@
       <c r="G57" t="n">
         <v>120</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5077,7 +5021,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5101,7 +5045,6 @@
       <c r="G58" t="n">
         <v>120</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5134,7 +5077,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5158,7 +5101,6 @@
       <c r="G59" t="n">
         <v>120</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5191,7 +5133,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5215,7 +5157,6 @@
       <c r="G60" t="n">
         <v>120</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5248,7 +5189,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5272,7 +5213,6 @@
       <c r="G61" t="n">
         <v>120</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5305,7 +5245,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5329,7 +5269,6 @@
       <c r="G62" t="n">
         <v>120</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5362,7 +5301,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5386,7 +5325,6 @@
       <c r="G63" t="n">
         <v>120</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5419,7 +5357,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5443,7 +5381,6 @@
       <c r="G64" t="n">
         <v>120</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5476,7 +5413,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5500,7 +5437,6 @@
       <c r="G65" t="n">
         <v>120</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5533,7 +5469,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5557,7 +5493,6 @@
       <c r="G66" t="n">
         <v>120</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5590,7 +5525,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5614,7 +5549,6 @@
       <c r="G67" t="n">
         <v>120</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5647,7 +5581,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5671,7 +5605,6 @@
       <c r="G68" t="n">
         <v>120</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5704,7 +5637,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5728,7 +5661,6 @@
       <c r="G69" t="n">
         <v>120</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5761,7 +5693,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5785,7 +5717,6 @@
       <c r="G70" t="n">
         <v>120</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5818,7 +5749,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5842,7 +5773,6 @@
       <c r="G71" t="n">
         <v>120</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5875,7 +5805,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5899,7 +5829,6 @@
       <c r="G72" t="n">
         <v>120</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5932,7 +5861,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5956,7 +5885,6 @@
       <c r="G73" t="n">
         <v>120</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5989,7 +5917,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6013,7 +5941,6 @@
       <c r="G74" t="n">
         <v>120</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6046,7 +5973,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6070,7 +5997,6 @@
       <c r="G75" t="n">
         <v>120</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6103,7 +6029,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6127,7 +6053,6 @@
       <c r="G76" t="n">
         <v>120</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6160,7 +6085,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6184,7 +6109,6 @@
       <c r="G77" t="n">
         <v>120</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6217,7 +6141,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6241,7 +6165,6 @@
       <c r="G78" t="n">
         <v>120</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6274,7 +6197,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6298,7 +6221,6 @@
       <c r="G79" t="n">
         <v>120</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6331,7 +6253,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6355,7 +6277,6 @@
       <c r="G80" t="n">
         <v>120</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6388,7 +6309,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6412,7 +6333,6 @@
       <c r="G81" t="n">
         <v>120</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6445,7 +6365,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6469,7 +6389,6 @@
       <c r="G82" t="n">
         <v>120</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6502,7 +6421,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6526,7 +6445,6 @@
       <c r="G83" t="n">
         <v>120</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6559,7 +6477,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6583,7 +6501,6 @@
       <c r="G84" t="n">
         <v>120</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6616,7 +6533,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6640,7 +6557,6 @@
       <c r="G85" t="n">
         <v>120</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6673,7 +6589,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6697,7 +6613,6 @@
       <c r="G86" t="n">
         <v>120</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6730,7 +6645,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6754,7 +6669,6 @@
       <c r="G87" t="n">
         <v>120</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6787,7 +6701,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6811,7 +6725,6 @@
       <c r="G88" t="n">
         <v>120</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6844,7 +6757,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6868,7 +6781,6 @@
       <c r="G89" t="n">
         <v>120</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6901,7 +6813,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6925,7 +6837,6 @@
       <c r="G90" t="n">
         <v>120</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6958,7 +6869,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6982,7 +6893,6 @@
       <c r="G91" t="n">
         <v>120</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7015,7 +6925,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7039,7 +6949,6 @@
       <c r="G92" t="n">
         <v>120</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7072,7 +6981,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7096,7 +7005,6 @@
       <c r="G93" t="n">
         <v>120</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7129,7 +7037,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7153,7 +7061,6 @@
       <c r="G94" t="n">
         <v>120</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7186,7 +7093,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7210,7 +7117,6 @@
       <c r="G95" t="n">
         <v>120</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7243,7 +7149,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7267,7 +7173,6 @@
       <c r="G96" t="n">
         <v>120</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7300,7 +7205,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Standalone Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7324,7 +7229,6 @@
       <c r="G97" t="n">
         <v>120</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -7381,7 +7285,6 @@
       <c r="G98" t="n">
         <v>857</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>

--- a/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
+++ b/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for belle-vie-new-zayed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1537,7 +1547,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1597,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1637,7 +1647,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1654,7 +1664,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1687,7 +1697,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1704,7 +1714,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1737,7 +1747,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1787,7 +1797,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1885,7 +1895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1919,7 +1929,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1941,7 +1951,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1975,7 +1985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1997,7 +2007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2031,7 +2041,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/10/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -4271,7 +4281,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4327,7 +4337,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4383,7 +4393,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4439,7 +4449,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4495,7 +4505,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4551,7 +4561,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4607,7 +4617,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4663,7 +4673,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4719,7 +4729,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4775,7 +4785,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4831,7 +4841,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4853,7 +4863,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4887,7 +4897,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4909,7 +4919,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4943,7 +4953,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4965,7 +4975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4999,7 +5009,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5021,7 +5031,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5055,7 +5065,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5077,7 +5087,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5111,7 +5121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5133,7 +5143,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5167,7 +5177,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5189,7 +5199,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5223,7 +5233,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5245,7 +5255,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5279,7 +5289,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5301,7 +5311,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5335,7 +5345,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5357,7 +5367,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5391,7 +5401,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5413,7 +5423,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5447,7 +5457,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5469,7 +5479,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5503,7 +5513,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5525,7 +5535,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5559,7 +5569,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5581,7 +5591,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5615,7 +5625,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5637,7 +5647,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5671,7 +5681,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5693,7 +5703,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5727,7 +5737,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5749,7 +5759,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5783,7 +5793,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5805,7 +5815,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5839,7 +5849,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5861,7 +5871,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5895,7 +5905,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5917,7 +5927,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5951,7 +5961,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5973,7 +5983,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6007,7 +6017,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6029,7 +6039,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6063,7 +6073,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6085,7 +6095,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6119,7 +6129,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6141,7 +6151,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6175,7 +6185,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6197,7 +6207,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6231,7 +6241,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6253,7 +6263,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6287,7 +6297,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6309,7 +6319,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6343,7 +6353,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6365,7 +6375,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6399,7 +6409,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6421,7 +6431,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6455,7 +6465,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6477,7 +6487,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6511,7 +6521,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6533,7 +6543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6567,7 +6577,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6589,7 +6599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6623,7 +6633,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6645,7 +6655,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6679,7 +6689,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6701,7 +6711,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6735,7 +6745,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6757,7 +6767,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6791,7 +6801,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6813,7 +6823,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6847,7 +6857,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6869,7 +6879,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6903,7 +6913,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6925,7 +6935,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6959,7 +6969,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6981,7 +6991,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7015,7 +7025,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7037,7 +7047,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7093,7 +7103,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7127,7 +7137,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7149,7 +7159,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7183,7 +7193,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7205,7 +7215,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One-Story Standalone Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7239,7 +7249,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>31/05/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7295,7 +7305,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">

--- a/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
+++ b/data/availability/projects/emaar-misr/belle-vie-new-zayed.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
